--- a/ksoft_old/docs/fields_details/Customer_Fields_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Customer_Fields_Detail.xlsx
@@ -1446,13 +1446,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53DED88C-67E3-417C-BE3C-C30845F22464}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B02D3D91-2E9C-4E9B-9507-B6DAA29194C5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBEF4B94-5886-4537-B36E-508DCF7C1F1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A045A71-AC99-4421-BAA1-0A9739E0A952}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C36A5B77-1E04-4810-9BF6-9275D56EE0E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357ABC2A-25E7-4F70-A967-F3905DACE607}"/>
 </file>
--- a/ksoft_old/docs/fields_details/Customer_Fields_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Customer_Fields_Detail.xlsx
@@ -1446,13 +1446,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B02D3D91-2E9C-4E9B-9507-B6DAA29194C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D953F84-088B-4959-895E-617647CC4891}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A045A71-AC99-4421-BAA1-0A9739E0A952}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3ED6705-752B-4A77-881B-E64B4C100C22}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357ABC2A-25E7-4F70-A967-F3905DACE607}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7DC6AA5-C05E-4E25-81DE-62B4F10AD1AC}"/>
 </file>
--- a/ksoft_old/docs/fields_details/Customer_Fields_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Customer_Fields_Detail.xlsx
@@ -1446,13 +1446,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D953F84-088B-4959-895E-617647CC4891}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53DED88C-67E3-417C-BE3C-C30845F22464}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3ED6705-752B-4A77-881B-E64B4C100C22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBEF4B94-5886-4537-B36E-508DCF7C1F1F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7DC6AA5-C05E-4E25-81DE-62B4F10AD1AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C36A5B77-1E04-4810-9BF6-9275D56EE0E2}"/>
 </file>